--- a/mapping_model_amef.xlsx
+++ b/mapping_model_amef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gestionare_clienti_cu SQLite\pythonProject1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89BA721-C1C5-4854-BDB9-BB19B65CFA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C6BBE4-AA9A-4DFA-98E8-262925D497D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/mapping_model_amef.xlsx
+++ b/mapping_model_amef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gestionare_clienti_cu SQLite\pythonProject1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C6BBE4-AA9A-4DFA-98E8-262925D497D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350E8939-6214-4375-A3E8-5072191F8ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -135,15 +135,9 @@
     <t>142</t>
   </si>
   <si>
-    <t>DATECS WP50-MX</t>
-  </si>
-  <si>
     <t>141</t>
   </si>
   <si>
-    <t>DATECS DP05MX</t>
-  </si>
-  <si>
     <t>164</t>
   </si>
   <si>
@@ -178,6 +172,12 @@
   </si>
   <si>
     <t>TREMOL M20 - VALMED</t>
+  </si>
+  <si>
+    <t>DATECS DP05 MX</t>
+  </si>
+  <si>
+    <t>DATECS WP50 MX</t>
   </si>
 </sst>
 </file>
@@ -530,7 +530,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -552,7 +552,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>18</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>27</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>31</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>31</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>34</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
@@ -783,10 +783,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C26" s="2">
         <v>44510</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2">
         <v>45127</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
